--- a/results/chronological/consolidated/Distributional_Metrics.xlsx
+++ b/results/chronological/consolidated/Distributional_Metrics.xlsx
@@ -571,9 +571,15 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
+      <c r="H8" t="n">
+        <v>4.70220879429418</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0760587657027125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.21576196612595</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -587,9 +593,15 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
+      <c r="H9" t="n">
+        <v>4.82938935533362</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0443173608043613</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.89439033311974</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -604,13 +616,13 @@
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10" t="n">
-        <v>4.70221284520177</v>
+        <v>5.0168560499265</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0760588337715788</v>
+        <v>-0.0267984152174368</v>
       </c>
       <c r="J10" t="n">
-        <v>3.21576198117375</v>
+        <v>2.97572767857793</v>
       </c>
     </row>
     <row r="11">
@@ -626,13 +638,13 @@
       <c r="F11"/>
       <c r="G11"/>
       <c r="H11" t="n">
-        <v>4.34824677072517</v>
+        <v>4.43362697994298</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0176444892631275</v>
+        <v>-0.00912646098742565</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2700554220282</v>
+        <v>3.08215603816632</v>
       </c>
     </row>
     <row r="12">
@@ -663,9 +675,15 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
+      <c r="H13" t="n">
+        <v>4.34824616072623</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.0176446368209284</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.27005530136216</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -680,13 +698,13 @@
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14" t="n">
-        <v>4.62740566413606</v>
+        <v>4.32305237284258</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0845907471959776</v>
+        <v>0.0226455568612981</v>
       </c>
       <c r="J14" t="n">
-        <v>3.09183332790868</v>
+        <v>3.20809839746819</v>
       </c>
     </row>
     <row r="15">
@@ -702,13 +720,13 @@
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15" t="n">
-        <v>4.69792859507493</v>
+        <v>4.78616047481064</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0494498092263679</v>
+        <v>0.0550909439200797</v>
       </c>
       <c r="J15" t="n">
-        <v>2.82717666470144</v>
+        <v>2.9397926207381</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +742,13 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16" t="n">
-        <v>4.78616345920606</v>
+        <v>4.38255775806272</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0550911656384521</v>
+        <v>0.00320758213754315</v>
       </c>
       <c r="J16" t="n">
-        <v>2.93979251316748</v>
+        <v>3.11009179221466</v>
       </c>
     </row>
     <row r="17">
@@ -746,13 +764,13 @@
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17" t="n">
-        <v>4.32305520625586</v>
+        <v>5.17659051824451</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0226457881741091</v>
+        <v>0.00116730560027024</v>
       </c>
       <c r="J17" t="n">
-        <v>3.20809839582789</v>
+        <v>2.85989006071627</v>
       </c>
     </row>
     <row r="18">
@@ -768,13 +786,13 @@
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18" t="n">
-        <v>5.05669417848952</v>
+        <v>4.61402142472866</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.00659873329894657</v>
+        <v>-0.0670696368203424</v>
       </c>
       <c r="J18" t="n">
-        <v>3.07700268617467</v>
+        <v>3.08439816961003</v>
       </c>
     </row>
     <row r="19">
@@ -790,13 +808,13 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" t="n">
-        <v>4.74222107504206</v>
+        <v>5.0566929467662</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0843909609408671</v>
+        <v>-0.00659874980122987</v>
       </c>
       <c r="J19" t="n">
-        <v>2.98569310264029</v>
+        <v>3.07700279531506</v>
       </c>
     </row>
     <row r="20">
@@ -812,13 +830,13 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" t="n">
-        <v>4.43362699200275</v>
+        <v>5.244650661473</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.00912637496253657</v>
+        <v>-0.0321198296846921</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0821559786722</v>
+        <v>2.9813744477186</v>
       </c>
     </row>
     <row r="21">
@@ -834,13 +852,13 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" t="n">
-        <v>5.01685960455178</v>
+        <v>4.96609490057701</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0267983855109663</v>
+        <v>-0.00227740859072289</v>
       </c>
       <c r="J21" t="n">
-        <v>2.97572759885331</v>
+        <v>2.86063254386816</v>
       </c>
     </row>
     <row r="22">
@@ -856,13 +874,13 @@
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" t="n">
-        <v>4.96609138518183</v>
+        <v>4.52995979652902</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.00227735876074971</v>
+        <v>-0.022571926929137</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86063267367456</v>
+        <v>2.95514136472821</v>
       </c>
     </row>
     <row r="23">
@@ -878,13 +896,13 @@
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23" t="n">
-        <v>5.24464901442457</v>
+        <v>4.74631490703734</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0321199280846539</v>
+        <v>0.0462547501277038</v>
       </c>
       <c r="J23" t="n">
-        <v>2.98137425687029</v>
+        <v>3.01836538341332</v>
       </c>
     </row>
     <row r="24">
@@ -900,13 +918,13 @@
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24" t="n">
-        <v>4.97505583277867</v>
+        <v>5.2373283414808</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0542904946301161</v>
+        <v>-0.101208098404603</v>
       </c>
       <c r="J24" t="n">
-        <v>2.97327647598687</v>
+        <v>2.90912741062335</v>
       </c>
     </row>
     <row r="25">
@@ -922,13 +940,13 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="n">
-        <v>4.82939094692155</v>
+        <v>4.97506293349294</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0443175195221486</v>
+        <v>-0.0542905957809496</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8943904104158</v>
+        <v>2.97327660763542</v>
       </c>
     </row>
   </sheetData>
@@ -999,13 +1017,13 @@
         <v>#NUM!</v>
       </c>
       <c r="I2" t="n">
-        <v>4.70557802970075</v>
+        <v>4.72317924924255</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0036480329237262</v>
+        <v>0.00140716698293648</v>
       </c>
       <c r="K2" t="n">
-        <v>3.02159944840341</v>
+        <v>3.04654563934372</v>
       </c>
     </row>
     <row r="3">
@@ -1030,13 +1048,13 @@
         <v>#NUM!</v>
       </c>
       <c r="I3" t="n">
-        <v>4.52522980796347</v>
+        <v>4.6660654680447</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0292071722542257</v>
+        <v>0.0133613226962566</v>
       </c>
       <c r="K3" t="n">
-        <v>3.24290870160097</v>
+        <v>3.08761826347042</v>
       </c>
     </row>
     <row r="4">
@@ -1061,13 +1079,13 @@
         <v>#NUM!</v>
       </c>
       <c r="I4" t="n">
-        <v>4.91094562931019</v>
+        <v>4.94990192343169</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0133825037378123</v>
+        <v>-0.0277021848770669</v>
       </c>
       <c r="K4" t="n">
-        <v>2.96125956574551</v>
+        <v>2.94965295966451</v>
       </c>
     </row>
     <row r="5">

--- a/results/chronological/consolidated/Distributional_Metrics.xlsx
+++ b/results/chronological/consolidated/Distributional_Metrics.xlsx
@@ -571,15 +571,9 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8"/>
-      <c r="H8" t="n">
-        <v>4.70220879429418</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0760587657027125</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.21576196612595</v>
-      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -593,15 +587,9 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
-      <c r="H9" t="n">
-        <v>4.82938935533362</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0443173608043613</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.89439033311974</v>
-      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -615,15 +603,9 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
-      <c r="H10" t="n">
-        <v>5.0168560499265</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.0267984152174368</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.97572767857793</v>
-      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -637,15 +619,9 @@
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
-      <c r="H11" t="n">
-        <v>4.43362697994298</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.00912646098742565</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.08215603816632</v>
-      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -675,15 +651,9 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13" t="n">
-        <v>4.34824616072623</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.0176446368209284</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.27005530136216</v>
-      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -697,15 +667,9 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
-      <c r="H14" t="n">
-        <v>4.32305237284258</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0226455568612981</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.20809839746819</v>
-      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -719,15 +683,9 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
-      <c r="H15" t="n">
-        <v>4.78616047481064</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0550909439200797</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.9397926207381</v>
-      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -741,15 +699,9 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
-      <c r="H16" t="n">
-        <v>4.38255775806272</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.00320758213754315</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.11009179221466</v>
-      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -763,15 +715,9 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17" t="n">
-        <v>5.17659051824451</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.00116730560027024</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.85989006071627</v>
-      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -785,15 +731,9 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
-      <c r="H18" t="n">
-        <v>4.61402142472866</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.0670696368203424</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.08439816961003</v>
-      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -807,15 +747,9 @@
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19"/>
-      <c r="H19" t="n">
-        <v>5.0566929467662</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.00659874980122987</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.07700279531506</v>
-      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -829,15 +763,9 @@
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
-      <c r="H20" t="n">
-        <v>5.244650661473</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.0321198296846921</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.9813744477186</v>
-      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -851,15 +779,9 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
-      <c r="H21" t="n">
-        <v>4.96609490057701</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.00227740859072289</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.86063254386816</v>
-      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -873,15 +795,9 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
-      <c r="H22" t="n">
-        <v>4.52995979652902</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.022571926929137</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.95514136472821</v>
-      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -895,15 +811,9 @@
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
-      <c r="H23" t="n">
-        <v>4.74631490703734</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0462547501277038</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.01836538341332</v>
-      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -917,15 +827,9 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24" t="n">
-        <v>5.2373283414808</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.101208098404603</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.90912741062335</v>
-      </c>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
@@ -939,15 +843,9 @@
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
-      <c r="H25" t="n">
-        <v>4.97506293349294</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.0542905957809496</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.97327660763542</v>
-      </c>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1016,14 +914,14 @@
       <c r="H2" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.72317924924255</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.00140716698293648</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.04654563934372</v>
+      <c r="I2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K2" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="3">
@@ -1047,14 +945,14 @@
       <c r="H3" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.6660654680447</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0133613226962566</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.08761826347042</v>
+      <c r="I3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K3" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4">
@@ -1078,14 +976,14 @@
       <c r="H4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="I4" t="n">
-        <v>4.94990192343169</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.0277021848770669</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.94965295966451</v>
+      <c r="I4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="K4" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="5">

--- a/results/chronological/consolidated/Distributional_Metrics.xlsx
+++ b/results/chronological/consolidated/Distributional_Metrics.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -54,13 +54,34 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -561,10 +582,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -577,10 +598,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
@@ -593,10 +614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -609,10 +630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -625,10 +646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -641,10 +662,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -657,10 +678,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -673,10 +694,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -689,10 +710,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -705,10 +726,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17"/>
       <c r="D17"/>
@@ -721,10 +742,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -737,10 +758,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19"/>
       <c r="D19"/>
@@ -753,10 +774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -769,10 +790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C21"/>
       <c r="D21"/>
@@ -785,10 +806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C22"/>
       <c r="D22"/>
@@ -801,10 +822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
         <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>14</v>
       </c>
       <c r="C23"/>
       <c r="D23"/>
@@ -817,10 +838,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C24"/>
       <c r="D24"/>
@@ -833,10 +854,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -846,6 +867,454 @@
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -863,39 +1332,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B2" t="e">
         <v>#NUM!</v>
@@ -926,7 +1395,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B3" t="e">
         <v>#NUM!</v>
@@ -957,7 +1426,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B4" t="e">
         <v>#NUM!</v>
